--- a/Documents/Character List.xlsx
+++ b/Documents/Character List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugob\BindingStories\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118345A3-7DD9-4279-B1C2-2BA09C82BD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B3342C-1EDB-4803-BD52-A8C5DD77FDE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="384">
   <si>
     <t>Name</t>
   </si>
@@ -1168,6 +1168,15 @@
   </si>
   <si>
     <t>Umbral Scholar ?</t>
+  </si>
+  <si>
+    <t>Ronie</t>
+  </si>
+  <si>
+    <t>0x3A</t>
+  </si>
+  <si>
+    <t>Spellsword 6</t>
   </si>
 </sst>
 </file>
@@ -2361,119 +2370,99 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>91</v>
+        <v>381</v>
       </c>
       <c r="B54" s="1">
         <v>9</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>92</v>
+        <v>382</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>93</v>
+        <v>383</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B55" s="1">
-        <v>9</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B56" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>288</v>
+        <v>93</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F56" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B57" s="1">
+        <v>10</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B58" s="1">
         <v>10</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>107</v>
+        <v>288</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B59" s="1">
-        <v>10</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="B60" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>308</v>
+        <v>107</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>192</v>
+        <v>10</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>23</v>
@@ -2481,19 +2470,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>191</v>
+        <v>101</v>
       </c>
       <c r="B61" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>194</v>
+        <v>106</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>192</v>
+        <v>10</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>23</v>
@@ -2501,99 +2490,99 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>259</v>
+        <v>172</v>
       </c>
       <c r="B62" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>260</v>
+        <v>173</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>174</v>
+        <v>308</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>10</v>
+        <v>192</v>
       </c>
       <c r="F62" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B63" s="1">
+        <v>11</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>103</v>
+        <v>259</v>
       </c>
       <c r="B64" s="1">
         <v>11</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>104</v>
+        <v>260</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>105</v>
+        <v>174</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B65" s="1">
-        <v>11</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B66" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>112</v>
+        <v>297</v>
       </c>
       <c r="B67" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>114</v>
+        <v>244</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>23</v>
@@ -2601,93 +2590,93 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>185</v>
+        <v>109</v>
       </c>
       <c r="B68" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>186</v>
+        <v>110</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>253</v>
+        <v>112</v>
       </c>
       <c r="B69" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>225</v>
+        <v>113</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>252</v>
+        <v>114</v>
       </c>
       <c r="E69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B70" s="1">
+        <v>12</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="B71" s="1">
         <v>12</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>79</v>
+        <v>225</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B72" s="1">
-        <v>12</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F72" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>131</v>
+        <v>232</v>
       </c>
       <c r="B73" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>10</v>
@@ -2698,124 +2687,124 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B74" s="1">
+        <v>13</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B75" s="1">
+        <v>13</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B74" s="1">
-        <v>12</v>
-      </c>
-      <c r="C74" s="1" t="s">
+      <c r="B76" s="1">
+        <v>13</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E75" s="1" t="s">
+      <c r="E76" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E77" s="1" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B77" s="1">
-        <v>13</v>
-      </c>
-      <c r="C77" s="1" t="s">
+      <c r="B79" s="1">
+        <v>14</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B78" s="1">
-        <v>13</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F78" s="1" t="s">
+      <c r="E79" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="B80" s="1">
         <v>14</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>298</v>
+        <v>10</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B81" s="1">
-        <v>14</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>126</v>
+        <v>234</v>
       </c>
       <c r="B82" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>10</v>
+        <v>298</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>23</v>
@@ -2823,167 +2812,167 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="B83" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>210</v>
+        <v>126</v>
       </c>
       <c r="B84" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>211</v>
+        <v>127</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>212</v>
+        <v>10</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B85" s="1">
+        <v>15</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="B86" s="1">
         <v>15</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B87" s="1">
-        <v>15</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>300</v>
+        <v>212</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>301</v>
+        <v>221</v>
       </c>
       <c r="B88" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>116</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>10</v>
+        <v>300</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="B89" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>303</v>
+        <v>229</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>23</v>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B90" s="1">
+        <v>16</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>148</v>
+        <v>233</v>
       </c>
       <c r="B91" s="1">
         <v>16</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>150</v>
+        <v>303</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B92" s="1">
-        <v>16</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F92" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B93" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>23</v>
@@ -2994,16 +2983,16 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>246</v>
+        <v>151</v>
       </c>
       <c r="B94" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>249</v>
+        <v>65</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>23</v>
@@ -3014,79 +3003,79 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="B95" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>141</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B96" s="1">
+        <v>17</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>205</v>
+        <v>138</v>
       </c>
       <c r="B97" s="1">
         <v>17</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>206</v>
+        <v>139</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>207</v>
+        <v>10</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B98" s="1">
-        <v>17</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="B99" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>270</v>
+        <v>93</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>23</v>
+        <v>207</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>23</v>
@@ -3094,99 +3083,99 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>242</v>
+        <v>135</v>
       </c>
       <c r="B100" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>201</v>
+        <v>136</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>243</v>
+        <v>137</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>238</v>
+        <v>23</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>238</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>239</v>
+        <v>179</v>
       </c>
       <c r="B101" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>115</v>
+        <v>180</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="E101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B102" s="1">
+        <v>18</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="F102" s="1" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="B103" s="1">
         <v>18</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>214</v>
+        <v>115</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>304</v>
+        <v>238</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B104" s="1">
-        <v>18</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>23</v>
+        <v>238</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="B105" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>209</v>
+        <v>304</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>23</v>
@@ -3194,19 +3183,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B106" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>247</v>
+        <v>176</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>204</v>
+        <v>10</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>23</v>
@@ -3214,230 +3203,253 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>256</v>
+        <v>144</v>
       </c>
       <c r="B107" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>257</v>
+        <v>146</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>10</v>
+        <v>209</v>
       </c>
       <c r="F107" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B108" s="1">
+        <v>19</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F108" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>358</v>
+        <v>256</v>
       </c>
       <c r="B109" s="1">
         <v>19</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>359</v>
+        <v>159</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>356</v>
+        <v>257</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>238</v>
+        <v>10</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>265</v>
+        <v>358</v>
       </c>
       <c r="B111" s="1">
         <v>20</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>266</v>
+        <v>356</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B112" s="1">
-        <v>20</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>23</v>
+        <v>238</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="B113" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>228</v>
+        <v>23</v>
       </c>
       <c r="F113" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B114" s="1">
+        <v>21</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>305</v>
+        <v>226</v>
       </c>
       <c r="B115" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B116" s="1">
-        <v>21</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>238</v>
+      <c r="C115" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="B117" s="1">
-        <v>21</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E117" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B118" s="1">
+        <v>22</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="B119" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B120" s="1">
-        <v>22</v>
+      <c r="C119" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>351</v>
+        <v>306</v>
       </c>
       <c r="B121" s="1">
-        <v>22</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>238</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B122" s="1">
+        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>377</v>
+        <v>351</v>
       </c>
       <c r="B123" s="1">
         <v>23</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>316</v>
+        <v>377</v>
       </c>
       <c r="B125" s="1">
         <v>24</v>
       </c>
-      <c r="C125" s="1" t="s">
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B127" s="1">
+        <v>25</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D127" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E125" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B126" s="1">
-        <v>24</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E126" s="1" t="s">
+      <c r="E127" s="1" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="B128" s="1">
         <v>25</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>238</v>
@@ -3445,101 +3457,84 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B130" s="1">
         <v>26</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B131" s="1">
-        <v>26</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="B132" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>238</v>
       </c>
     </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B133" s="1">
+        <v>27</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>313</v>
+        <v>368</v>
       </c>
       <c r="B134" s="1">
         <v>27</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>315</v>
+        <v>370</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B135" s="1">
-        <v>27</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="B136" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>238</v>
@@ -3547,16 +3542,16 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>371</v>
+        <v>16</v>
       </c>
       <c r="B137" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>372</v>
+        <v>17</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>373</v>
+        <v>18</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>238</v>
@@ -3564,33 +3559,50 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="B138" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>379</v>
+        <v>334</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>238</v>
       </c>
     </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B139" s="1">
+        <v>28</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>335</v>
+        <v>378</v>
       </c>
       <c r="B140" s="1">
         <v>28</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>336</v>
+        <v>379</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>238</v>
@@ -3598,47 +3610,47 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="B142" s="1">
         <v>29</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A143" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B143" s="1">
-        <v>29</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="E143" s="1" t="s">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B144" s="1">
+        <v>30</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E144" s="1" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B145" s="1">
         <v>30</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>319</v>
@@ -3649,16 +3661,16 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="B147" s="1">
         <v>31</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>238</v>
@@ -3666,109 +3678,121 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B149" s="1">
         <v>32</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>357</v>
+        <v>238</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="B151" s="1">
         <v>33</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>238</v>
+        <v>357</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>343</v>
+        <v>374</v>
       </c>
       <c r="B153" s="1">
         <v>34</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>344</v>
+        <v>375</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>345</v>
+        <v>238</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="B155" s="1">
         <v>35</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>10</v>
+        <v>345</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B157" s="1">
         <v>36</v>
       </c>
       <c r="C157" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B159" s="1">
+        <v>37</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D157" s="1" t="s">
+      <c r="D159" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="E157" s="1" t="s">
+      <c r="E159" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A158" s="1" t="s">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B158" s="1">
-        <v>36</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B160" s="1">
         <v>37</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
@@ -3777,25 +3801,25 @@
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A164" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="B164" s="1">
         <v>39</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>238</v>
-      </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
+        <v>363</v>
+      </c>
       <c r="B166" s="1">
         <v>40</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/Character List.xlsx
+++ b/Documents/Character List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugob\BindingStories\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B3342C-1EDB-4803-BD52-A8C5DD77FDE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEFFB8C-2C76-4EBF-84C9-B533FD1B5660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="453">
   <si>
     <t>Name</t>
   </si>
@@ -39,9 +39,6 @@
     <t>Class &amp; Level</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>Celindra</t>
   </si>
   <si>
@@ -60,9 +57,6 @@
     <t>Joins on Turn 1.</t>
   </si>
   <si>
-    <t>Lord Unit (Game Over)</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
@@ -84,9 +78,6 @@
     <t>Spear Champion 27</t>
   </si>
   <si>
-    <t>Game Over Unit. Leaves at the end of the chapter.</t>
-  </si>
-  <si>
     <t>Aline</t>
   </si>
   <si>
@@ -126,9 +117,6 @@
     <t>Automatic Recruitment at the end of Turn 1.</t>
   </si>
   <si>
-    <t>Mandatory to recruit Cilicia.</t>
-  </si>
-  <si>
     <t>Apatheia</t>
   </si>
   <si>
@@ -150,9 +138,6 @@
     <t>Archer 3</t>
   </si>
   <si>
-    <t>Game Over Unit on its joining chapter.</t>
-  </si>
-  <si>
     <t>Samaël</t>
   </si>
   <si>
@@ -183,9 +168,6 @@
     <t>Talk with any Lord or Brad.</t>
   </si>
   <si>
-    <t>Game Over Unit.</t>
-  </si>
-  <si>
     <t>Brad</t>
   </si>
   <si>
@@ -204,9 +186,6 @@
     <t>Talk with Apatheia.</t>
   </si>
   <si>
-    <t>Mandatory to recruit Sarin.</t>
-  </si>
-  <si>
     <t>Theoria</t>
   </si>
   <si>
@@ -234,9 +213,6 @@
     <t>Pirate 5</t>
   </si>
   <si>
-    <t>Makes an appearance as an NPC in Prologue.</t>
-  </si>
-  <si>
     <t>0x19</t>
   </si>
   <si>
@@ -402,12 +378,6 @@
     <t>0x2A</t>
   </si>
   <si>
-    <t>Baron 2</t>
-  </si>
-  <si>
-    <t>Larry</t>
-  </si>
-  <si>
     <t>0x36</t>
   </si>
   <si>
@@ -450,9 +420,6 @@
     <t>Sword General 2</t>
   </si>
   <si>
-    <t>Recruited if given a second chance on Interlude 1.</t>
-  </si>
-  <si>
     <t>Alicianrone</t>
   </si>
   <si>
@@ -540,9 +507,6 @@
     <t>0x23</t>
   </si>
   <si>
-    <t>Archer 5</t>
-  </si>
-  <si>
     <t>Ascilia</t>
   </si>
   <si>
@@ -636,9 +600,6 @@
     <t>Krilalaris</t>
   </si>
   <si>
-    <t>Archer ?</t>
-  </si>
-  <si>
     <t>Free from her cell and pay 50 gold.</t>
   </si>
   <si>
@@ -798,9 +759,6 @@
     <t>Estelle</t>
   </si>
   <si>
-    <t>Sniper 4</t>
-  </si>
-  <si>
     <t>Druid 2</t>
   </si>
   <si>
@@ -849,9 +807,6 @@
     <t>Dirue</t>
   </si>
   <si>
-    <t>Have him survive the chapter.</t>
-  </si>
-  <si>
     <t>Appears as a reinforcement. Talk with Celindra.</t>
   </si>
   <si>
@@ -945,9 +900,6 @@
     <t>Aurora</t>
   </si>
   <si>
-    <t>[Theocracy Ruler]</t>
-  </si>
-  <si>
     <t>Lisa</t>
   </si>
   <si>
@@ -963,9 +915,6 @@
     <t>0x2C</t>
   </si>
   <si>
-    <t>Axe General ?</t>
-  </si>
-  <si>
     <t>Héloïse</t>
   </si>
   <si>
@@ -1177,6 +1126,264 @@
   </si>
   <si>
     <t>Spellsword 6</t>
+  </si>
+  <si>
+    <t>Kelsey</t>
+  </si>
+  <si>
+    <t>0x47</t>
+  </si>
+  <si>
+    <t>Soldier 6</t>
+  </si>
+  <si>
+    <t>Enris</t>
+  </si>
+  <si>
+    <t>0x7E</t>
+  </si>
+  <si>
+    <t>Shaman 2</t>
+  </si>
+  <si>
+    <t>Erhardt</t>
+  </si>
+  <si>
+    <t>George</t>
+  </si>
+  <si>
+    <t>Gersao</t>
+  </si>
+  <si>
+    <t>0x84</t>
+  </si>
+  <si>
+    <t>0x88</t>
+  </si>
+  <si>
+    <t>Lance Paladin 4</t>
+  </si>
+  <si>
+    <t>Axe Paladin 4</t>
+  </si>
+  <si>
+    <t>0x8B</t>
+  </si>
+  <si>
+    <t>Shaman ?</t>
+  </si>
+  <si>
+    <t>Probably a Village Visit</t>
+  </si>
+  <si>
+    <t>0x8E</t>
+  </si>
+  <si>
+    <t>Warmaiden ?</t>
+  </si>
+  <si>
+    <t>Vermouth</t>
+  </si>
+  <si>
+    <t>0x8F</t>
+  </si>
+  <si>
+    <t>Baron ?</t>
+  </si>
+  <si>
+    <t>Holly</t>
+  </si>
+  <si>
+    <t>0x90</t>
+  </si>
+  <si>
+    <t>Lance General 1</t>
+  </si>
+  <si>
+    <t>Vega</t>
+  </si>
+  <si>
+    <t>0x93</t>
+  </si>
+  <si>
+    <t>0x8A</t>
+  </si>
+  <si>
+    <t>0x31</t>
+  </si>
+  <si>
+    <t>Kettei</t>
+  </si>
+  <si>
+    <t>Laila</t>
+  </si>
+  <si>
+    <t>Enstir</t>
+  </si>
+  <si>
+    <t>Magiquiver 5</t>
+  </si>
+  <si>
+    <t>0x8C</t>
+  </si>
+  <si>
+    <t>0x7A</t>
+  </si>
+  <si>
+    <t>Aenir</t>
+  </si>
+  <si>
+    <t>0x62</t>
+  </si>
+  <si>
+    <t>Manakete ?</t>
+  </si>
+  <si>
+    <t>0x96</t>
+  </si>
+  <si>
+    <t>Warmaiden 1</t>
+  </si>
+  <si>
+    <t>0x97</t>
+  </si>
+  <si>
+    <t>0x99</t>
+  </si>
+  <si>
+    <t>0x9A</t>
+  </si>
+  <si>
+    <t>Destio</t>
+  </si>
+  <si>
+    <t>Asty</t>
+  </si>
+  <si>
+    <t>Effris</t>
+  </si>
+  <si>
+    <t>0x9D</t>
+  </si>
+  <si>
+    <t>Dancer ?</t>
+  </si>
+  <si>
+    <t>Spellranger ?</t>
+  </si>
+  <si>
+    <t>Crimecaster ?</t>
+  </si>
+  <si>
+    <t>0x9E</t>
+  </si>
+  <si>
+    <t>Lance General ?</t>
+  </si>
+  <si>
+    <t>Start of Chapter.</t>
+  </si>
+  <si>
+    <t>Pandore</t>
+  </si>
+  <si>
+    <t>0xA1</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>0xA2</t>
+  </si>
+  <si>
+    <t>Lance Cavalier 6</t>
+  </si>
+  <si>
+    <t>0xA3</t>
+  </si>
+  <si>
+    <t>0xA4</t>
+  </si>
+  <si>
+    <t>0xA5</t>
+  </si>
+  <si>
+    <t>Sword Cavalier ?</t>
+  </si>
+  <si>
+    <t>0x9C</t>
+  </si>
+  <si>
+    <t>Tactician ?</t>
+  </si>
+  <si>
+    <t>Ryia</t>
+  </si>
+  <si>
+    <t>Gennevote</t>
+  </si>
+  <si>
+    <t>Imbertus</t>
+  </si>
+  <si>
+    <t>Triena</t>
+  </si>
+  <si>
+    <t>Reginald</t>
+  </si>
+  <si>
+    <t>Raimund</t>
+  </si>
+  <si>
+    <t>François</t>
+  </si>
+  <si>
+    <t>Falcoknight 2</t>
+  </si>
+  <si>
+    <t>Ritsu</t>
+  </si>
+  <si>
+    <t>Yvon</t>
+  </si>
+  <si>
+    <t>Joins if spared.</t>
+  </si>
+  <si>
+    <t>Leche</t>
+  </si>
+  <si>
+    <t>Swordmaster 5</t>
+  </si>
+  <si>
+    <t>Private 6</t>
+  </si>
+  <si>
+    <t>Swordmaster 4</t>
+  </si>
+  <si>
+    <t>0x8D</t>
+  </si>
+  <si>
+    <t>Spellranger 1</t>
+  </si>
+  <si>
+    <t>Spellranger 4</t>
+  </si>
+  <si>
+    <t>Axe General 16</t>
+  </si>
+  <si>
+    <t>Bow Armor 10</t>
+  </si>
+  <si>
+    <t>Sorcerer 3</t>
+  </si>
+  <si>
+    <t>Hero 15</t>
+  </si>
+  <si>
+    <t>Magiquiver 13</t>
   </si>
 </sst>
 </file>
@@ -1497,7 +1704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:E189"/>
   <sheetFormatPr defaultColWidth="22" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" style="1"/>
@@ -1505,11 +1712,10 @@
     <col min="3" max="3" width="6" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="76.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="54.21875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="22" style="1"/>
+    <col min="6" max="16384" width="22" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1517,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -1525,2301 +1731,2449 @@
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="B11" s="1">
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B12" s="1">
         <v>2</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1">
         <v>3</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1">
         <v>3</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B16" s="1">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1">
         <v>3</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="B18" s="1">
         <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="B19" s="1">
         <v>3</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B21" s="1">
         <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B22" s="1">
         <v>4</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B23" s="1">
         <v>4</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="B24" s="1">
         <v>4</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="B25" s="1">
         <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="B26" s="1">
         <v>4</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="B28" s="1">
         <v>5</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B29" s="1">
         <v>5</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>273</v>
+        <v>59</v>
       </c>
       <c r="B30" s="1">
         <v>5</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B31" s="1">
         <v>5</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B32" s="1">
         <v>5</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="B34" s="1">
         <v>6</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B35" s="1">
         <v>6</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B36" s="1">
         <v>6</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="B37" s="1">
         <v>6</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="B38" s="1">
         <v>6</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="B39" s="1">
         <v>6</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="B40" s="1">
         <v>6</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="B42" s="1">
         <v>7</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="B43" s="1">
         <v>7</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>171</v>
+        <v>398</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="B44" s="1">
         <v>7</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B45" s="1">
         <v>7</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B46" s="1">
         <v>7</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B48" s="1">
         <v>8</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B49" s="1">
         <v>8</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="B50" s="1">
         <v>8</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B51" s="1">
         <v>8</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="B52" s="1">
         <v>8</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B54" s="1">
+        <v>9</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B55" s="1">
+        <v>9</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B56" s="1">
+        <v>9</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B57" s="1">
+        <v>9</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B58" s="1">
+        <v>9</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B60" s="1">
+        <v>10</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B61" s="1">
+        <v>10</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="B62" s="1">
+        <v>10</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B54" s="1">
-        <v>9</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="E54" s="1" t="s">
+      <c r="D62" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B63" s="1">
         <v>10</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
+      <c r="C63" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B56" s="1">
-        <v>10</v>
-      </c>
-      <c r="C56" s="1" t="s">
+      <c r="B65" s="1">
+        <v>11</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D65" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
+      <c r="B66" s="1">
+        <v>11</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B57" s="1">
-        <v>10</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B58" s="1">
-        <v>10</v>
-      </c>
-      <c r="C58" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B60" s="1">
+      <c r="E66" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B67" s="1">
         <v>11</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B61" s="1">
+      <c r="C67" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B68" s="1">
         <v>11</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B62" s="1">
+      <c r="C68" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B69" s="1">
         <v>11</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B63" s="1">
-        <v>11</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
+      <c r="C69" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="B64" s="1">
-        <v>11</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B66" s="1">
-        <v>12</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B67" s="1">
-        <v>12</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B68" s="1">
-        <v>12</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B69" s="1">
-        <v>12</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B70" s="1">
-        <v>12</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="B71" s="1">
         <v>12</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>225</v>
+        <v>62</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>252</v>
+        <v>63</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B72" s="1">
+        <v>12</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>232</v>
+        <v>101</v>
       </c>
       <c r="B73" s="1">
+        <v>12</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B74" s="1">
+        <v>12</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B75" s="1">
+        <v>12</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B76" s="1">
+        <v>12</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B78" s="1">
         <v>13</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B74" s="1">
+      <c r="C78" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B79" s="1">
         <v>13</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B75" s="1">
+      <c r="C79" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B80" s="1">
         <v>13</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B76" s="1">
+      <c r="C80" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B81" s="1">
         <v>13</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E77" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B79" s="1">
-        <v>14</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B80" s="1">
-        <v>14</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C81" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>234</v>
+        <v>123</v>
       </c>
       <c r="B82" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>124</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>125</v>
+        <v>287</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B83" s="1">
-        <v>15</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>157</v>
-      </c>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E83" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B84" s="1">
-        <v>15</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>162</v>
+        <v>396</v>
       </c>
       <c r="B85" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>210</v>
+        <v>397</v>
       </c>
       <c r="B86" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>211</v>
+        <v>111</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>221</v>
       </c>
       <c r="B88" s="1">
+        <v>15</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B89" s="1">
+        <v>15</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B90" s="1">
+        <v>15</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B91" s="1">
+        <v>15</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B92" s="1">
+        <v>15</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="1">
         <v>16</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B89" s="1">
+      <c r="C94" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" s="1">
         <v>16</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D89" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B96" s="1">
+        <v>16</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B97" s="1">
+        <v>16</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B99" s="1">
+        <v>17</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B100" s="1">
+        <v>17</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B101" s="1">
+        <v>17</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B102" s="1">
+        <v>17</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B103" s="1">
+        <v>17</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B104" s="1">
+        <v>17</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B106" s="1">
+        <v>18</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B107" s="1">
+        <v>18</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B90" s="1">
-        <v>16</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B91" s="1">
-        <v>16</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E91" s="1" t="s">
+      <c r="B108" s="1">
+        <v>18</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B109" s="1">
+        <v>18</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B111" s="1">
+        <v>19</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B112" s="1">
+        <v>19</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B113" s="1">
+        <v>19</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B114" s="1">
+        <v>19</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B115" s="1">
+        <v>19</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B116" s="1">
+        <v>19</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B118" s="1">
+        <v>20</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B120" s="1">
+        <v>21</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B121" s="1">
+        <v>21</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B122" s="1">
+        <v>21</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B124" s="1">
+        <v>22</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B125" s="1">
+        <v>22</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B126" s="1">
+        <v>22</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B127" s="1">
+        <v>22</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B129" s="1">
         <v>23</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B93" s="1">
-        <v>17</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B94" s="1">
-        <v>17</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B95" s="1">
-        <v>17</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B96" s="1">
-        <v>17</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B97" s="1">
-        <v>17</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B99" s="1">
-        <v>18</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B100" s="1">
-        <v>18</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B101" s="1">
-        <v>18</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B102" s="1">
-        <v>18</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B103" s="1">
-        <v>18</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B105" s="1">
-        <v>19</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B106" s="1">
-        <v>19</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B107" s="1">
-        <v>19</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B108" s="1">
-        <v>19</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B109" s="1">
-        <v>19</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="B111" s="1">
-        <v>20</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B113" s="1">
-        <v>21</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B114" s="1">
-        <v>21</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B115" s="1">
-        <v>21</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B117" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B118" s="1">
-        <v>22</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B119" s="1">
-        <v>22</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="B121" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B122" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B123" s="1">
-        <v>23</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="B125" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="B127" s="1">
-        <v>25</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B128" s="1">
-        <v>25</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>238</v>
+      <c r="C129" s="1" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>340</v>
+        <v>291</v>
       </c>
       <c r="B130" s="1">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>238</v>
+        <v>394</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B131" s="1">
+        <v>23</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>346</v>
+        <v>438</v>
       </c>
       <c r="B132" s="1">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A133" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B133" s="1">
-        <v>27</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>238</v>
+        <v>382</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B134" s="1">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>238</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B135" s="1">
+        <v>24</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>313</v>
+        <v>374</v>
       </c>
       <c r="B136" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>314</v>
+        <v>376</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>315</v>
+        <v>378</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>238</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>16</v>
+        <v>375</v>
       </c>
       <c r="B137" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>17</v>
+        <v>377</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>18</v>
+        <v>379</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B138" s="1">
-        <v>28</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>238</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>371</v>
+        <v>299</v>
       </c>
       <c r="B139" s="1">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>372</v>
+        <v>300</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>373</v>
+        <v>302</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>378</v>
+        <v>303</v>
       </c>
       <c r="B140" s="1">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>379</v>
+        <v>301</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>380</v>
+        <v>304</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>238</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B141" s="1">
+        <v>25</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>335</v>
+        <v>410</v>
       </c>
       <c r="B142" s="1">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>336</v>
+        <v>407</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A144" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B144" s="1">
-        <v>30</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>238</v>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B143" s="1">
+        <v>25</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B145" s="1">
+        <v>26</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B145" s="1">
-        <v>30</v>
-      </c>
-      <c r="C145" s="1" t="s">
+      <c r="D145" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D145" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="E145" s="1" t="s">
-        <v>238</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B146" s="1">
+        <v>26</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>326</v>
+        <v>436</v>
       </c>
       <c r="B147" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>327</v>
+        <v>426</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>319</v>
+        <v>427</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>238</v>
+        <v>345</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B149" s="1">
+        <v>27</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B150" s="1">
+        <v>27</v>
+      </c>
+      <c r="C150" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B149" s="1">
-        <v>32</v>
-      </c>
-      <c r="C149" s="1" t="s">
+      <c r="D150" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D149" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>238</v>
+      <c r="E150" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B151" s="1">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A153" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="B153" s="1">
-        <v>34</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>238</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B152" s="1">
+        <v>27</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B154" s="1">
+        <v>28</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>343</v>
+        <v>14</v>
       </c>
       <c r="B155" s="1">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>344</v>
+        <v>15</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>342</v>
+        <v>16</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>345</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B156" s="1">
+        <v>28</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>328</v>
+        <v>361</v>
       </c>
       <c r="B157" s="1">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>319</v>
+        <v>363</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>10</v>
+        <v>225</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="B159" s="1">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="B160" s="1">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>270</v>
+        <v>384</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>362</v>
+        <v>225</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>294</v>
+      </c>
       <c r="B162" s="1">
-        <v>38</v>
+        <v>30</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B163" s="1">
+        <v>30</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
+        <v>385</v>
+      </c>
       <c r="B164" s="1">
-        <v>39</v>
+        <v>30</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="B166" s="1">
+        <v>31</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B167" s="1">
+        <v>31</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B169" s="1">
+        <v>32</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B171" s="1">
+        <v>33</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B172" s="1">
+        <v>33</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B174" s="1">
+        <v>34</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B175" s="1">
+        <v>34</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B177" s="1">
+        <v>35</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B178" s="1">
+        <v>35</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B180" s="1">
+        <v>36</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A182" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B182" s="1">
+        <v>37</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A183" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B183" s="1">
+        <v>37</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B185" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B187" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A189" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B189" s="1">
         <v>40</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>238</v>
+      <c r="C189" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/Character List.xlsx
+++ b/Documents/Character List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugob\BindingStories\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEFFB8C-2C76-4EBF-84C9-B533FD1B5660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDA592E-F013-4ED4-A18B-7FFBB34CEDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="456">
   <si>
     <t>Name</t>
   </si>
@@ -1384,6 +1384,15 @@
   </si>
   <si>
     <t>Magiquiver 13</t>
+  </si>
+  <si>
+    <t>Cid</t>
+  </si>
+  <si>
+    <t>0x9B</t>
+  </si>
+  <si>
+    <t>Magiquiver 8</t>
   </si>
 </sst>
 </file>
@@ -1704,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E189"/>
+  <dimension ref="A1:E190"/>
   <sheetFormatPr defaultColWidth="22" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" style="1"/>
@@ -2850,16 +2859,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>121</v>
+        <v>453</v>
       </c>
       <c r="B81" s="1">
         <v>13</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>122</v>
+        <v>454</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>58</v>
+        <v>455</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>9</v>
@@ -2867,106 +2876,106 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B82" s="1">
         <v>13</v>
       </c>
       <c r="C82" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B83" s="1">
+        <v>13</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D83" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E83" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E84" s="1" t="s">
         <v>284</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="B85" s="1">
-        <v>14</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B86" s="1">
         <v>14</v>
       </c>
       <c r="C86" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B87" s="1">
+        <v>14</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B88" s="1">
-        <v>15</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>283</v>
+      <c r="E87" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="B89" s="1">
         <v>15</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>146</v>
+        <v>437</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>9</v>
+        <v>283</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="B90" s="1">
         <v>15</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>9</v>
@@ -2974,67 +2983,67 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="B91" s="1">
         <v>15</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>199</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>391</v>
+        <v>197</v>
       </c>
       <c r="B92" s="1">
         <v>15</v>
       </c>
       <c r="C92" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B93" s="1">
+        <v>15</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E93" s="1" t="s">
         <v>225</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B94" s="1">
-        <v>16</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B95" s="1">
         <v>16</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>285</v>
@@ -3042,67 +3051,67 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>286</v>
+        <v>210</v>
       </c>
       <c r="B96" s="1">
         <v>16</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>9</v>
+        <v>285</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="B97" s="1">
         <v>16</v>
       </c>
       <c r="C97" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B98" s="1">
+        <v>16</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="D98" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B99" s="1">
-        <v>17</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E99" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B100" s="1">
         <v>17</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>446</v>
+        <v>139</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>20</v>
@@ -3110,16 +3119,16 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B101" s="1">
         <v>17</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>144</v>
+        <v>446</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>20</v>
@@ -3127,16 +3136,16 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="B102" s="1">
         <v>17</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>236</v>
+        <v>144</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>20</v>
@@ -3144,316 +3153,316 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>128</v>
+        <v>233</v>
       </c>
       <c r="B103" s="1">
         <v>17</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>440</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>441</v>
+        <v>128</v>
       </c>
       <c r="B104" s="1">
         <v>17</v>
       </c>
       <c r="C104" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B105" s="1">
+        <v>17</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="D105" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E105" s="1" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B106" s="1">
-        <v>18</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="B107" s="1">
         <v>18</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>126</v>
+        <v>193</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>20</v>
+        <v>194</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>229</v>
+        <v>125</v>
       </c>
       <c r="B108" s="1">
         <v>18</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>230</v>
+        <v>127</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>225</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B109" s="1">
         <v>18</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>107</v>
+        <v>189</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B111" s="1">
-        <v>19</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>289</v>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B110" s="1">
+        <v>18</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B112" s="1">
         <v>19</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>244</v>
+        <v>202</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>9</v>
+        <v>289</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="B113" s="1">
         <v>19</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>135</v>
+        <v>244</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>196</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>190</v>
+        <v>133</v>
       </c>
       <c r="B114" s="1">
         <v>19</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>234</v>
+        <v>134</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>452</v>
+        <v>135</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="B115" s="1">
         <v>19</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>9</v>
+        <v>191</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>316</v>
+        <v>243</v>
       </c>
       <c r="B116" s="1">
         <v>19</v>
       </c>
       <c r="C116" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B117" s="1">
+        <v>19</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D117" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
+      <c r="E117" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B118" s="1">
+      <c r="B119" s="1">
         <v>20</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>225</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B120" s="1">
-        <v>21</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>293</v>
+        <v>251</v>
       </c>
       <c r="B121" s="1">
         <v>21</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>238</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>213</v>
+        <v>293</v>
       </c>
       <c r="B122" s="1">
         <v>21</v>
       </c>
       <c r="C122" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B123" s="1">
+        <v>21</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D123" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="E123" s="1" t="s">
         <v>215</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="B124" s="1">
-        <v>22</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B125" s="1">
         <v>22</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>225</v>
+        <v>393</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B126" s="1">
         <v>22</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>442</v>
+        <v>302</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>225</v>
@@ -3461,103 +3470,103 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>167</v>
+        <v>313</v>
       </c>
       <c r="B127" s="1">
         <v>22</v>
       </c>
       <c r="C127" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B128" s="1">
+        <v>22</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D128" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="E128" s="1" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="B129" s="1">
-        <v>23</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>291</v>
+        <v>439</v>
       </c>
       <c r="B130" s="1">
         <v>23</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>334</v>
+        <v>291</v>
       </c>
       <c r="B131" s="1">
         <v>23</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>225</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>438</v>
+        <v>334</v>
       </c>
       <c r="B132" s="1">
         <v>23</v>
       </c>
       <c r="C132" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B133" s="1">
+        <v>23</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D133" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="E132" s="1" t="s">
+      <c r="E133" s="1" t="s">
         <v>382</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A134" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="B134" s="1">
-        <v>24</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="B135" s="1">
         <v>24</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>118</v>
+        <v>400</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>20</v>
@@ -3565,16 +3574,16 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B136" s="1">
         <v>24</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>376</v>
+        <v>117</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>378</v>
+        <v>118</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>20</v>
@@ -3582,50 +3591,50 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B137" s="1">
         <v>24</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A139" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B139" s="1">
-        <v>25</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>225</v>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B138" s="1">
+        <v>24</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B140" s="1">
         <v>25</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>225</v>
@@ -3633,75 +3642,75 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>409</v>
+        <v>303</v>
       </c>
       <c r="B141" s="1">
         <v>25</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>406</v>
+        <v>301</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>336</v>
+        <v>304</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B142" s="1">
         <v>25</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>413</v>
+        <v>336</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B143" s="1">
         <v>25</v>
       </c>
       <c r="C143" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B144" s="1">
+        <v>25</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="D144" s="1" t="s">
         <v>414</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B145" s="1">
-        <v>26</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>419</v>
+        <v>323</v>
       </c>
       <c r="B146" s="1">
         <v>26</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>420</v>
+        <v>324</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>443</v>
+        <v>325</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>225</v>
@@ -3709,50 +3718,50 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="B147" s="1">
         <v>26</v>
       </c>
       <c r="C147" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B148" s="1">
+        <v>26</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="D148" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="E147" s="1" t="s">
+      <c r="E148" s="1" t="s">
         <v>345</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A149" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B149" s="1">
-        <v>27</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="B150" s="1">
         <v>27</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>225</v>
@@ -3760,16 +3769,16 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B151" s="1">
         <v>27</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>225</v>
@@ -3777,50 +3786,50 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>430</v>
+        <v>351</v>
       </c>
       <c r="B152" s="1">
         <v>27</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>428</v>
+        <v>352</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>429</v>
+        <v>353</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A154" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B154" s="1">
-        <v>28</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E154" s="1" t="s">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B153" s="1">
+        <v>27</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>14</v>
+        <v>296</v>
       </c>
       <c r="B155" s="1">
         <v>28</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>15</v>
+        <v>297</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>16</v>
+        <v>298</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>225</v>
@@ -3828,16 +3837,16 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>354</v>
+        <v>14</v>
       </c>
       <c r="B156" s="1">
         <v>28</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>355</v>
+        <v>15</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>356</v>
+        <v>16</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>225</v>
@@ -3845,84 +3854,84 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B157" s="1">
         <v>28</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A159" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B159" s="1">
-        <v>29</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E159" s="1" t="s">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B158" s="1">
+        <v>28</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>395</v>
+        <v>318</v>
       </c>
       <c r="B160" s="1">
         <v>29</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>383</v>
+        <v>319</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>384</v>
+        <v>315</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A162" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B162" s="1">
-        <v>30</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="E162" s="1" t="s">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A161" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B161" s="1">
+        <v>29</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="B163" s="1">
         <v>30</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>225</v>
@@ -3930,249 +3939,266 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>385</v>
+        <v>307</v>
       </c>
       <c r="B164" s="1">
         <v>30</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>386</v>
+        <v>308</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>387</v>
+        <v>451</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A166" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B166" s="1">
-        <v>31</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E166" s="1" t="s">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B165" s="1">
+        <v>30</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>401</v>
+        <v>309</v>
       </c>
       <c r="B167" s="1">
         <v>31</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>402</v>
+        <v>310</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>403</v>
+        <v>302</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A169" s="1" t="s">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B168" s="1">
+        <v>31</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B169" s="1">
+      <c r="B170" s="1">
         <v>32</v>
       </c>
-      <c r="C169" s="1" t="s">
+      <c r="C170" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D169" s="1" t="s">
+      <c r="D170" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="E169" s="1" t="s">
+      <c r="E170" s="1" t="s">
         <v>225</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A171" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B171" s="1">
-        <v>33</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>431</v>
+        <v>337</v>
       </c>
       <c r="B172" s="1">
         <v>33</v>
       </c>
       <c r="C172" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B173" s="1">
+        <v>33</v>
+      </c>
+      <c r="C173" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D172" s="1" t="s">
+      <c r="D173" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="E172" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A174" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B174" s="1">
-        <v>34</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="E174" s="1" t="s">
+      <c r="E173" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>435</v>
+        <v>357</v>
       </c>
       <c r="B175" s="1">
         <v>34</v>
       </c>
       <c r="C175" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B176" s="1">
+        <v>34</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D175" s="1" t="s">
+      <c r="D176" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="E175" s="1" t="s">
+      <c r="E176" s="1" t="s">
         <v>345</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A177" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B177" s="1">
-        <v>35</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>432</v>
+        <v>326</v>
       </c>
       <c r="B178" s="1">
         <v>35</v>
       </c>
       <c r="C178" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B179" s="1">
+        <v>35</v>
+      </c>
+      <c r="C179" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D178" s="1" t="s">
+      <c r="D179" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E178" s="1" t="s">
+      <c r="E179" s="1" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A180" s="1" t="s">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A181" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B180" s="1">
+      <c r="B181" s="1">
         <v>36</v>
       </c>
-      <c r="C180" s="1" t="s">
+      <c r="C181" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="D180" s="1" t="s">
+      <c r="D181" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E180" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A182" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B182" s="1">
-        <v>37</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>225</v>
+      <c r="E181" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="B183" s="1">
         <v>37</v>
       </c>
       <c r="C183" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A184" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B184" s="1">
+        <v>37</v>
+      </c>
+      <c r="C184" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D183" s="1" t="s">
+      <c r="D184" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E183" s="1" t="s">
+      <c r="E184" s="1" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B185" s="1">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B186" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B187" s="1">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B188" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A189" s="1" t="s">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A190" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B189" s="1">
+      <c r="B190" s="1">
         <v>40</v>
       </c>
-      <c r="C189" s="1" t="s">
+      <c r="C190" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="D190" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E189" s="1" t="s">
+      <c r="E190" s="1" t="s">
         <v>225</v>
       </c>
     </row>

--- a/Documents/Character List.xlsx
+++ b/Documents/Character List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugob\BindingStories\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDA592E-F013-4ED4-A18B-7FFBB34CEDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8702A356-14D9-4570-A0D4-78BDABD7799A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="458">
   <si>
     <t>Name</t>
   </si>
@@ -732,9 +732,6 @@
     <t>0x6E</t>
   </si>
   <si>
-    <t>Fighter 4</t>
-  </si>
-  <si>
     <t>Pegasus Knight 12</t>
   </si>
   <si>
@@ -858,9 +855,6 @@
     <t>0x4A</t>
   </si>
   <si>
-    <t>Cleric 6</t>
-  </si>
-  <si>
     <t>Velnorte</t>
   </si>
   <si>
@@ -1296,9 +1290,6 @@
     <t>0xA2</t>
   </si>
   <si>
-    <t>Lance Cavalier 6</t>
-  </si>
-  <si>
     <t>0xA3</t>
   </si>
   <si>
@@ -1386,13 +1377,28 @@
     <t>Magiquiver 13</t>
   </si>
   <si>
-    <t>Cid</t>
-  </si>
-  <si>
-    <t>0x9B</t>
-  </si>
-  <si>
-    <t>Magiquiver 8</t>
+    <t>Fighter 9</t>
+  </si>
+  <si>
+    <t>Initiate 6</t>
+  </si>
+  <si>
+    <t>Bow Cavalier 6</t>
+  </si>
+  <si>
+    <t>Peat</t>
+  </si>
+  <si>
+    <t>Wyvern Rider ?</t>
+  </si>
+  <si>
+    <t>Fanilye</t>
+  </si>
+  <si>
+    <t>0x9F</t>
+  </si>
+  <si>
+    <t>Sword Pegasus ?</t>
   </si>
 </sst>
 </file>
@@ -1713,7 +1719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E190"/>
+  <dimension ref="A1:E191"/>
   <sheetFormatPr defaultColWidth="22" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" style="1"/>
@@ -1794,7 +1800,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -1803,7 +1809,7 @@
         <v>166</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>9</v>
@@ -1990,7 +1996,7 @@
         <v>67</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>9</v>
@@ -2007,7 +2013,7 @@
         <v>154</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>9</v>
@@ -2075,7 +2081,7 @@
         <v>206</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>207</v>
@@ -2095,7 +2101,7 @@
         <v>224</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -2117,53 +2123,53 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>56</v>
+        <v>186</v>
       </c>
       <c r="B29" s="1">
         <v>5</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>57</v>
+        <v>187</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>9</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B30" s="1">
         <v>5</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>260</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>186</v>
+        <v>59</v>
       </c>
       <c r="B31" s="1">
         <v>5</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>187</v>
+        <v>60</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>188</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -2180,12 +2186,12 @@
         <v>66</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B34" s="1">
         <v>6</v>
@@ -2194,7 +2200,7 @@
         <v>149</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>225</v>
@@ -2245,7 +2251,7 @@
         <v>150</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>235</v>
+        <v>450</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>9</v>
@@ -2253,7 +2259,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B38" s="1">
         <v>6</v>
@@ -2262,32 +2268,32 @@
         <v>147</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B39" s="1">
         <v>6</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>277</v>
+        <v>451</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B40" s="1">
         <v>6</v>
@@ -2296,24 +2302,24 @@
         <v>136</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B42" s="1">
         <v>7</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>9</v>
@@ -2330,24 +2336,24 @@
         <v>159</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B44" s="1">
         <v>7</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>9</v>
@@ -2355,16 +2361,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B45" s="1">
         <v>7</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>9</v>
@@ -2384,7 +2390,7 @@
         <v>120</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -2469,21 +2475,21 @@
         <v>82</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B54" s="1">
+        <v>9</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="B54" s="1">
-        <v>9</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>366</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>9</v>
@@ -2491,16 +2497,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B55" s="1">
+        <v>9</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="B55" s="1">
-        <v>9</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>20</v>
@@ -2508,16 +2514,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B56" s="1">
+        <v>9</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="B56" s="1">
-        <v>9</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>20</v>
@@ -2525,16 +2531,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B57" s="1">
+        <v>9</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="B57" s="1">
-        <v>9</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>390</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>20</v>
@@ -2542,50 +2548,50 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B58" s="1">
         <v>9</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>423</v>
+        <v>452</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B60" s="1">
-        <v>10</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>9</v>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B59" s="1">
+        <v>9</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B61" s="1">
         <v>10</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>9</v>
@@ -2593,16 +2599,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B62" s="1">
         <v>10</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>273</v>
+        <v>88</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>9</v>
@@ -2610,44 +2616,44 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>434</v>
+        <v>89</v>
       </c>
       <c r="B63" s="1">
         <v>10</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B65" s="1">
-        <v>11</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>9</v>
+        <v>90</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B64" s="1">
+        <v>10</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B66" s="1">
         <v>11</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>9</v>
@@ -2655,33 +2661,33 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>160</v>
+        <v>93</v>
       </c>
       <c r="B67" s="1">
         <v>11</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>161</v>
+        <v>94</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>292</v>
+        <v>98</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>180</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="B68" s="1">
         <v>11</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>182</v>
+        <v>290</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>180</v>
@@ -2689,67 +2695,67 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>245</v>
+        <v>179</v>
       </c>
       <c r="B69" s="1">
         <v>11</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>246</v>
+        <v>181</v>
       </c>
       <c r="D69" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B70" s="1">
+        <v>11</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B71" s="1">
-        <v>12</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>20</v>
+      <c r="E70" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="B72" s="1">
         <v>12</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>231</v>
+        <v>63</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="B73" s="1">
         <v>12</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>103</v>
+        <v>231</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>9</v>
@@ -2757,33 +2763,33 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B74" s="1">
         <v>12</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>173</v>
+        <v>104</v>
       </c>
       <c r="B75" s="1">
         <v>12</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>174</v>
+        <v>105</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>20</v>
@@ -2791,87 +2797,87 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>240</v>
+        <v>173</v>
       </c>
       <c r="B76" s="1">
         <v>12</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>239</v>
+        <v>175</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B78" s="1">
-        <v>13</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>9</v>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B77" s="1">
+        <v>12</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="B79" s="1">
         <v>13</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>172</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>433</v>
+        <v>169</v>
       </c>
       <c r="B80" s="1">
         <v>13</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>404</v>
+        <v>170</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>405</v>
+        <v>171</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>20</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="B81" s="1">
         <v>13</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>454</v>
+        <v>402</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>455</v>
+        <v>403</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -2902,7 +2908,7 @@
         <v>124</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>9</v>
@@ -2910,12 +2916,12 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E84" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B86" s="1">
         <v>14</v>
@@ -2932,7 +2938,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B87" s="1">
         <v>14</v>
@@ -2958,10 +2964,10 @@
         <v>116</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -3017,16 +3023,16 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B93" s="1">
         <v>15</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>225</v>
@@ -3046,7 +3052,7 @@
         <v>108</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -3063,12 +3069,12 @@
         <v>216</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B97" s="1">
         <v>16</v>
@@ -3094,7 +3100,7 @@
         <v>145</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>20</v>
@@ -3128,7 +3134,7 @@
         <v>141</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>20</v>
@@ -3162,7 +3168,7 @@
         <v>163</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>20</v>
@@ -3182,18 +3188,18 @@
         <v>130</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B105" s="1">
         <v>17</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>135</v>
@@ -3284,7 +3290,7 @@
         <v>202</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -3298,7 +3304,7 @@
         <v>164</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>9</v>
@@ -3332,7 +3338,7 @@
         <v>234</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>191</v>
@@ -3340,7 +3346,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B116" s="1">
         <v>19</v>
@@ -3349,7 +3355,7 @@
         <v>148</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>9</v>
@@ -3357,16 +3363,16 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B117" s="1">
         <v>19</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>9</v>
@@ -3374,16 +3380,16 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B119" s="1">
         <v>20</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>225</v>
@@ -3391,7 +3397,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B121" s="1">
         <v>21</v>
@@ -3400,7 +3406,7 @@
         <v>18</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>20</v>
@@ -3408,7 +3414,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B122" s="1">
         <v>21</v>
@@ -3417,10 +3423,10 @@
         <v>204</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -3434,7 +3440,7 @@
         <v>214</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>215</v>
@@ -3442,27 +3448,27 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B125" s="1">
         <v>22</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B126" s="1">
         <v>22</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>225</v>
@@ -3470,16 +3476,16 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B127" s="1">
         <v>22</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>225</v>
@@ -3496,7 +3502,7 @@
         <v>168</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>20</v>
@@ -3504,38 +3510,38 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B130" s="1">
         <v>23</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B131" s="1">
         <v>23</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B132" s="1">
         <v>23</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>225</v>
@@ -3543,30 +3549,30 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B133" s="1">
         <v>23</v>
       </c>
       <c r="C133" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B135" s="1">
         <v>24</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>20</v>
@@ -3574,7 +3580,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B136" s="1">
         <v>24</v>
@@ -3591,16 +3597,16 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B137" s="1">
         <v>24</v>
       </c>
       <c r="C137" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>20</v>
@@ -3608,16 +3614,16 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B138" s="1">
         <v>24</v>
       </c>
       <c r="C138" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>20</v>
@@ -3625,16 +3631,16 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B140" s="1">
         <v>25</v>
       </c>
       <c r="C140" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>302</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>225</v>
@@ -3642,16 +3648,16 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B141" s="1">
         <v>25</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>225</v>
@@ -3659,58 +3665,58 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B142" s="1">
         <v>25</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B143" s="1">
         <v>25</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B144" s="1">
         <v>25</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B146" s="1">
         <v>26</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>225</v>
@@ -3718,16 +3724,16 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B147" s="1">
         <v>26</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>225</v>
@@ -3735,33 +3741,33 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B148" s="1">
         <v>26</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B150" s="1">
         <v>27</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>225</v>
@@ -3769,16 +3775,16 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B151" s="1">
         <v>27</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>225</v>
@@ -3786,16 +3792,16 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B152" s="1">
         <v>27</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>225</v>
@@ -3803,16 +3809,16 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B153" s="1">
         <v>27</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>225</v>
@@ -3820,16 +3826,16 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B155" s="1">
         <v>28</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>225</v>
@@ -3854,16 +3860,16 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B157" s="1">
         <v>28</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>225</v>
@@ -3871,16 +3877,16 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B158" s="1">
         <v>28</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>225</v>
@@ -3888,16 +3894,16 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B160" s="1">
         <v>29</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>225</v>
@@ -3905,50 +3911,50 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B161" s="1">
         <v>29</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A163" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B163" s="1">
-        <v>30</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="E163" s="1" t="s">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B162" s="1">
+        <v>29</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="B164" s="1">
         <v>30</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>225</v>
@@ -3956,249 +3962,266 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>385</v>
+        <v>305</v>
       </c>
       <c r="B165" s="1">
         <v>30</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>386</v>
+        <v>306</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>387</v>
+        <v>448</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A167" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B167" s="1">
-        <v>31</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E167" s="1" t="s">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B166" s="1">
+        <v>30</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>401</v>
+        <v>307</v>
       </c>
       <c r="B168" s="1">
         <v>31</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>402</v>
+        <v>308</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>403</v>
+        <v>300</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A170" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B170" s="1">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B169" s="1">
+        <v>31</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B171" s="1">
         <v>32</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D170" s="1" t="s">
+      <c r="C171" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="E170" s="1" t="s">
+      <c r="D171" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E171" s="1" t="s">
         <v>225</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A172" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B172" s="1">
-        <v>33</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>431</v>
+        <v>335</v>
       </c>
       <c r="B173" s="1">
         <v>33</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>412</v>
+        <v>336</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>415</v>
+        <v>337</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A175" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B175" s="1">
-        <v>34</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="E175" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B174" s="1">
+        <v>33</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E174" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>435</v>
+        <v>355</v>
       </c>
       <c r="B176" s="1">
         <v>34</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>425</v>
+        <v>356</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A178" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B178" s="1">
-        <v>35</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>328</v>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B177" s="1">
+        <v>34</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>432</v>
+        <v>324</v>
       </c>
       <c r="B179" s="1">
         <v>35</v>
       </c>
       <c r="C179" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B180" s="1">
+        <v>35</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D179" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A181" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="B181" s="1">
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A182" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B182" s="1">
         <v>36</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A183" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B183" s="1">
-        <v>37</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>225</v>
+      <c r="C182" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="B184" s="1">
         <v>37</v>
       </c>
       <c r="C184" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A185" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B185" s="1">
+        <v>37</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B187" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B189" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A191" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D184" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E184" s="1" t="s">
+      <c r="B191" s="1">
+        <v>40</v>
+      </c>
+      <c r="C191" s="1" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B186" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B188" s="1">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A190" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B190" s="1">
-        <v>40</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E190" s="1" t="s">
+      <c r="D191" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>225</v>
       </c>
     </row>

--- a/Documents/Character List.xlsx
+++ b/Documents/Character List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugob\BindingStories\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8702A356-14D9-4570-A0D4-78BDABD7799A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70961574-65D9-4118-B06F-70CBB7CC6579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="440">
   <si>
     <t>Name</t>
   </si>
@@ -204,15 +204,6 @@
     <t>Sniper 1</t>
   </si>
   <si>
-    <t>Leon</t>
-  </si>
-  <si>
-    <t>0x1B</t>
-  </si>
-  <si>
-    <t>Pirate 5</t>
-  </si>
-  <si>
     <t>0x19</t>
   </si>
   <si>
@@ -246,15 +237,6 @@
     <t>Sword Armor 6</t>
   </si>
   <si>
-    <t>Alicia</t>
-  </si>
-  <si>
-    <t>0x1E</t>
-  </si>
-  <si>
-    <t>Shaman 5</t>
-  </si>
-  <si>
     <t>0x06</t>
   </si>
   <si>
@@ -312,15 +294,6 @@
     <t>0x05</t>
   </si>
   <si>
-    <t>Suguri</t>
-  </si>
-  <si>
-    <t>0x5A</t>
-  </si>
-  <si>
-    <t>Myrmidon 9</t>
-  </si>
-  <si>
     <t>Bow Armor 7</t>
   </si>
   <si>
@@ -486,12 +459,6 @@
     <t>0x12</t>
   </si>
   <si>
-    <t>Isabell</t>
-  </si>
-  <si>
-    <t>0x1A</t>
-  </si>
-  <si>
     <t>Blanche</t>
   </si>
   <si>
@@ -585,15 +552,6 @@
     <t>Wyvern Rider 3</t>
   </si>
   <si>
-    <t>Hime</t>
-  </si>
-  <si>
-    <t>0x6C</t>
-  </si>
-  <si>
-    <t>Automatically recruited during the second part of the map.</t>
-  </si>
-  <si>
     <t>0x6D</t>
   </si>
   <si>
@@ -795,18 +753,12 @@
     <t>???</t>
   </si>
   <si>
-    <t>Spellthief 3</t>
-  </si>
-  <si>
     <t>Thug 3</t>
   </si>
   <si>
     <t>Dirue</t>
   </si>
   <si>
-    <t>Appears as a reinforcement. Talk with Celindra.</t>
-  </si>
-  <si>
     <t>Visit her village.</t>
   </si>
   <si>
@@ -816,9 +768,6 @@
     <t>0x78</t>
   </si>
   <si>
-    <t>Supplier 5</t>
-  </si>
-  <si>
     <t>Probably NPC</t>
   </si>
   <si>
@@ -1113,24 +1062,6 @@
     <t>Umbral Scholar ?</t>
   </si>
   <si>
-    <t>Ronie</t>
-  </si>
-  <si>
-    <t>0x3A</t>
-  </si>
-  <si>
-    <t>Spellsword 6</t>
-  </si>
-  <si>
-    <t>Kelsey</t>
-  </si>
-  <si>
-    <t>0x47</t>
-  </si>
-  <si>
-    <t>Soldier 6</t>
-  </si>
-  <si>
     <t>Enris</t>
   </si>
   <si>
@@ -1399,6 +1330,21 @@
   </si>
   <si>
     <t>Sword Pegasus ?</t>
+  </si>
+  <si>
+    <t>Supplier 8</t>
+  </si>
+  <si>
+    <t>REMOVED CHARACTERS</t>
+  </si>
+  <si>
+    <t>Hime, Suguri, Leon (Ch5)</t>
+  </si>
+  <si>
+    <t>Isabell (Ch4)</t>
+  </si>
+  <si>
+    <t>Alicia (Ch6)</t>
   </si>
 </sst>
 </file>
@@ -1719,7 +1665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E191"/>
+  <dimension ref="A1:G184"/>
   <sheetFormatPr defaultColWidth="22" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" style="1"/>
@@ -1730,7 +1676,7 @@
     <col min="6" max="16384" width="22" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1746,8 +1692,11 @@
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G1" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1763,8 +1712,11 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G2" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1780,8 +1732,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G3" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1797,25 +1752,28 @@
       <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G4" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -1832,7 +1790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -1849,7 +1807,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -1866,7 +1824,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -1883,24 +1841,24 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B12" s="1">
         <v>2</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
@@ -1917,7 +1875,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -1934,7 +1892,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>53</v>
       </c>
@@ -1970,16 +1928,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="B18" s="1">
         <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>33</v>
@@ -1987,16 +1945,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="B19" s="1">
         <v>3</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>9</v>
@@ -2004,254 +1962,237 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
       <c r="B21" s="1">
         <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>256</v>
+        <v>45</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B22" s="1">
         <v>4</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>47</v>
+        <v>203</v>
       </c>
       <c r="B23" s="1">
         <v>4</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="B24" s="1">
         <v>4</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B25" s="1">
         <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>257</v>
+        <v>210</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B26" s="1">
-        <v>4</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>236</v>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="1">
+        <v>5</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="B28" s="1">
         <v>5</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B29" s="1">
-        <v>5</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>188</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>56</v>
+        <v>256</v>
       </c>
       <c r="B30" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>58</v>
+        <v>224</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B31" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>259</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>64</v>
+        <v>218</v>
       </c>
       <c r="B32" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>66</v>
+        <v>427</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>260</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B33" s="1">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="B34" s="1">
         <v>6</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>149</v>
+        <v>258</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>238</v>
+        <v>428</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>68</v>
+        <v>259</v>
       </c>
       <c r="B35" s="1">
         <v>6</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" s="1">
-        <v>6</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>9</v>
+        <v>262</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B37" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>9</v>
@@ -2259,101 +2200,101 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>252</v>
+        <v>147</v>
       </c>
       <c r="B38" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>253</v>
+        <v>373</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>274</v>
+        <v>249</v>
       </c>
       <c r="B39" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>451</v>
+        <v>251</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>278</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="B40" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B42" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" s="1">
         <v>7</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>9</v>
+      <c r="C41" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>158</v>
+        <v>13</v>
       </c>
       <c r="B43" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>159</v>
+        <v>70</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>396</v>
+        <v>71</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>266</v>
+        <v>72</v>
       </c>
       <c r="B44" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>267</v>
+        <v>73</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>268</v>
+        <v>74</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>9</v>
@@ -2361,135 +2302,135 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
       <c r="B45" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>270</v>
+        <v>145</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>271</v>
+        <v>146</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="B46" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B48" s="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B47" s="1">
         <v>8</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>9</v>
+      <c r="E47" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>78</v>
+        <v>345</v>
       </c>
       <c r="B49" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>155</v>
+        <v>363</v>
       </c>
       <c r="B50" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>156</v>
+        <v>364</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>157</v>
+        <v>365</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>225</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>176</v>
+        <v>396</v>
       </c>
       <c r="B51" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>177</v>
+        <v>397</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>178</v>
+        <v>429</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>225</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>228</v>
+        <v>430</v>
       </c>
       <c r="B52" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>81</v>
+        <v>381</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>246</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>362</v>
+        <v>77</v>
       </c>
       <c r="B54" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>363</v>
+        <v>78</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>364</v>
+        <v>79</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>9</v>
@@ -2497,163 +2438,163 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>365</v>
+        <v>80</v>
       </c>
       <c r="B55" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>368</v>
+        <v>83</v>
       </c>
       <c r="B56" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>369</v>
+        <v>84</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>370</v>
+        <v>255</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="B57" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="B58" s="1">
-        <v>9</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>20</v>
+        <v>398</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>453</v>
+        <v>85</v>
       </c>
       <c r="B59" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>404</v>
+        <v>86</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>454</v>
+        <v>90</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B60" s="1">
+        <v>11</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="B61" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>85</v>
+        <v>273</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>9</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>86</v>
+        <v>168</v>
       </c>
       <c r="B62" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>87</v>
+        <v>170</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>9</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>89</v>
+        <v>230</v>
       </c>
       <c r="B63" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>90</v>
+        <v>231</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>272</v>
+        <v>151</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="B64" s="1">
-        <v>10</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>421</v>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B65" s="1">
+        <v>12</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B66" s="1">
+        <v>12</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B66" s="1">
-        <v>11</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="D66" s="1" t="s">
-        <v>99</v>
+        <v>217</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>9</v>
@@ -2661,16 +2602,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" s="1">
+        <v>12</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B67" s="1">
-        <v>11</v>
-      </c>
-      <c r="C67" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>9</v>
@@ -2678,169 +2619,157 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="B68" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>290</v>
+        <v>97</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>180</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="B69" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>180</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="B70" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>245</v>
+        <v>198</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="B72" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>280</v>
+        <v>158</v>
       </c>
       <c r="B73" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>231</v>
+        <v>160</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>9</v>
+        <v>161</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>101</v>
+        <v>407</v>
       </c>
       <c r="B74" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>102</v>
+        <v>379</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>103</v>
+        <v>380</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B75" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>173</v>
+        <v>114</v>
       </c>
       <c r="B76" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>175</v>
+        <v>268</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B77" s="1">
-        <v>12</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E77" s="1" t="s">
-        <v>20</v>
+        <v>265</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>219</v>
+        <v>371</v>
       </c>
       <c r="B79" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>9</v>
@@ -2848,140 +2777,152 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>169</v>
+        <v>372</v>
       </c>
       <c r="B80" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="B81" s="1">
-        <v>13</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>121</v>
+        <v>207</v>
       </c>
       <c r="B82" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>58</v>
+        <v>411</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B83" s="1">
+        <v>15</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B83" s="1">
-        <v>13</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="D83" s="1" t="s">
-        <v>285</v>
+        <v>137</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B84" s="1">
+        <v>15</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="E84" s="1" t="s">
-        <v>282</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B85" s="1">
+        <v>15</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>394</v>
+        <v>366</v>
       </c>
       <c r="B86" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>109</v>
+        <v>367</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>110</v>
+        <v>423</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B87" s="1">
-        <v>14</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>9</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B88" s="1">
+        <v>16</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="B89" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>116</v>
+        <v>197</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>434</v>
+        <v>202</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>131</v>
+        <v>267</v>
       </c>
       <c r="B90" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>146</v>
+        <v>99</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>9</v>
@@ -2989,118 +2930,118 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="B91" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>118</v>
+        <v>269</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B92" s="1">
-        <v>15</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>199</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>389</v>
+        <v>128</v>
       </c>
       <c r="B93" s="1">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>390</v>
+        <v>129</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>446</v>
+        <v>130</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>225</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B94" s="1">
+        <v>17</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c r="B95" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>209</v>
+        <v>134</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>283</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B96" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>283</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>284</v>
+        <v>119</v>
       </c>
       <c r="B97" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>204</v>
+        <v>120</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>9</v>
+        <v>414</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>220</v>
+        <v>415</v>
       </c>
       <c r="B98" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>145</v>
+        <v>419</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>286</v>
+        <v>126</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>20</v>
@@ -3108,33 +3049,33 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="B100" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>20</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="B101" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>443</v>
+        <v>118</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>20</v>
@@ -3142,1087 +3083,985 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="B102" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>144</v>
+        <v>216</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>20</v>
+        <v>211</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="B103" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>163</v>
+        <v>98</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B104" s="1">
-        <v>17</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>437</v>
+        <v>211</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>438</v>
+        <v>186</v>
       </c>
       <c r="B105" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>442</v>
+        <v>187</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>20</v>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B106" s="1">
+        <v>19</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="B107" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>193</v>
+        <v>125</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="B108" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>126</v>
+        <v>220</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>127</v>
+        <v>426</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>20</v>
+        <v>177</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B109" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>230</v>
+        <v>421</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>225</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>226</v>
+        <v>297</v>
       </c>
       <c r="B110" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>107</v>
+        <v>298</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>227</v>
+        <v>418</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>225</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>200</v>
+        <v>322</v>
       </c>
       <c r="B112" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>201</v>
+        <v>323</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>202</v>
+        <v>320</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B113" s="1">
-        <v>19</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>9</v>
+        <v>211</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>133</v>
+        <v>236</v>
       </c>
       <c r="B114" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>135</v>
+        <v>237</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>196</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B115" s="1">
+        <v>21</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B115" s="1">
-        <v>19</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="D115" s="1" t="s">
-        <v>449</v>
+        <v>226</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="B116" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>444</v>
+        <v>227</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B117" s="1">
-        <v>19</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>9</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B118" s="1">
+        <v>22</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="B119" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>340</v>
+        <v>287</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>337</v>
+        <v>283</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B120" s="1">
+        <v>22</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>250</v>
+        <v>156</v>
       </c>
       <c r="B121" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>18</v>
+        <v>157</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>251</v>
+        <v>424</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B122" s="1">
-        <v>21</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>213</v>
+        <v>413</v>
       </c>
       <c r="B123" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>215</v>
+        <v>374</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B124" s="1">
+        <v>23</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="B125" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>391</v>
+        <v>316</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>303</v>
+        <v>412</v>
       </c>
       <c r="B126" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>300</v>
+        <v>356</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="B127" s="1">
-        <v>22</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>225</v>
+        <v>357</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>167</v>
+        <v>341</v>
       </c>
       <c r="B128" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>447</v>
+        <v>375</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>20</v>
       </c>
     </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B129" s="1">
+        <v>24</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>436</v>
+        <v>349</v>
       </c>
       <c r="B130" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>397</v>
+        <v>351</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="B131" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B132" s="1">
-        <v>23</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>225</v>
+        <v>352</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>435</v>
+        <v>280</v>
       </c>
       <c r="B133" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>378</v>
+        <v>281</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>379</v>
+        <v>283</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>380</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B134" s="1">
+        <v>25</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="B135" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>20</v>
+        <v>381</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B136" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>117</v>
+        <v>382</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>20</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="B137" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B138" s="1">
-        <v>24</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>20</v>
+        <v>389</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B139" s="1">
+        <v>26</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>297</v>
+        <v>394</v>
       </c>
       <c r="B140" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>298</v>
+        <v>395</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>300</v>
+        <v>417</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>301</v>
+        <v>410</v>
       </c>
       <c r="B141" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>299</v>
+        <v>400</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>302</v>
+        <v>401</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A142" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="B142" s="1">
-        <v>25</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>408</v>
+        <v>310</v>
       </c>
       <c r="B143" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>405</v>
+        <v>311</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>411</v>
+        <v>312</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>409</v>
+        <v>329</v>
       </c>
       <c r="B144" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>406</v>
+        <v>330</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>412</v>
+        <v>331</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B145" s="1">
+        <v>27</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>321</v>
+        <v>404</v>
       </c>
       <c r="B146" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>322</v>
+        <v>402</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>323</v>
+        <v>403</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A147" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="B147" s="1">
-        <v>26</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>433</v>
+        <v>277</v>
       </c>
       <c r="B148" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>423</v>
+        <v>278</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>424</v>
+        <v>279</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>343</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B149" s="1">
+        <v>28</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B150" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B151" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A152" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="B152" s="1">
-        <v>27</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>427</v>
+        <v>299</v>
       </c>
       <c r="B153" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>425</v>
+        <v>300</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>426</v>
+        <v>296</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B154" s="1">
+        <v>29</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>294</v>
+        <v>432</v>
       </c>
       <c r="B155" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>295</v>
+        <v>433</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>296</v>
+        <v>434</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A156" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B156" s="1">
-        <v>28</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>352</v>
+        <v>275</v>
       </c>
       <c r="B157" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>353</v>
+        <v>276</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>354</v>
+        <v>422</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>359</v>
+        <v>288</v>
       </c>
       <c r="B158" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C158" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="B159" s="1">
+        <v>30</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="E158" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A160" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="B160" s="1">
-        <v>29</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>225</v>
+      <c r="D159" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>393</v>
+        <v>290</v>
       </c>
       <c r="B161" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>381</v>
+        <v>291</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>382</v>
+        <v>283</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>455</v>
+        <v>376</v>
       </c>
       <c r="B162" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>456</v>
+        <v>377</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>457</v>
+        <v>378</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="B164" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>445</v>
+        <v>312</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A165" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B165" s="1">
-        <v>30</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>383</v>
+        <v>318</v>
       </c>
       <c r="B166" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>384</v>
+        <v>319</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>385</v>
+        <v>320</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A168" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B168" s="1">
-        <v>31</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>225</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B167" s="1">
+        <v>33</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B169" s="1">
+        <v>34</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B170" s="1">
+        <v>34</v>
+      </c>
+      <c r="C170" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B169" s="1">
-        <v>31</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A171" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B171" s="1">
-        <v>32</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>225</v>
+      <c r="D170" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B172" s="1">
+        <v>35</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>335</v>
+        <v>406</v>
       </c>
       <c r="B173" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>336</v>
+        <v>391</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>337</v>
+        <v>392</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A174" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="B174" s="1">
-        <v>33</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A176" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B176" s="1">
-        <v>34</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>225</v>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B175" s="1">
+        <v>36</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
-        <v>432</v>
+        <v>301</v>
       </c>
       <c r="B177" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>422</v>
+        <v>302</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>385</v>
+        <v>303</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A179" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B179" s="1">
-        <v>35</v>
-      </c>
-      <c r="C179" s="1" t="s">
+      <c r="B178" s="1">
+        <v>37</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D179" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="E179" s="1" t="s">
+      <c r="D178" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A180" s="1" t="s">
-        <v>429</v>
-      </c>
       <c r="B180" s="1">
-        <v>35</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>416</v>
+        <v>38</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A182" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="B182" s="1">
-        <v>36</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B184" s="1">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>320</v>
+        <v>241</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A185" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B185" s="1">
-        <v>37</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B187" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B189" s="1">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A191" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="B191" s="1">
-        <v>40</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/Character List.xlsx
+++ b/Documents/Character List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugob\BindingStories\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70961574-65D9-4118-B06F-70CBB7CC6579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685A3785-68EA-4B31-9C45-BDAAF22ED4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="417">
   <si>
     <t>Name</t>
   </si>
@@ -468,12 +468,6 @@
     <t>Light Mage 6</t>
   </si>
   <si>
-    <t>Alesia</t>
-  </si>
-  <si>
-    <t>0x23</t>
-  </si>
-  <si>
     <t>Ascilia</t>
   </si>
   <si>
@@ -768,9 +762,6 @@
     <t>0x78</t>
   </si>
   <si>
-    <t>Probably NPC</t>
-  </si>
-  <si>
     <t>Joins on Turn 1; will be available here and there in the following chapters.</t>
   </si>
   <si>
@@ -1062,15 +1053,6 @@
     <t>Umbral Scholar ?</t>
   </si>
   <si>
-    <t>Enris</t>
-  </si>
-  <si>
-    <t>0x7E</t>
-  </si>
-  <si>
-    <t>Shaman 2</t>
-  </si>
-  <si>
     <t>Erhardt</t>
   </si>
   <si>
@@ -1146,9 +1128,6 @@
     <t>Enstir</t>
   </si>
   <si>
-    <t>Magiquiver 5</t>
-  </si>
-  <si>
     <t>0x8C</t>
   </si>
   <si>
@@ -1164,39 +1143,9 @@
     <t>Manakete ?</t>
   </si>
   <si>
-    <t>0x96</t>
-  </si>
-  <si>
-    <t>Warmaiden 1</t>
-  </si>
-  <si>
-    <t>0x97</t>
-  </si>
-  <si>
-    <t>0x99</t>
-  </si>
-  <si>
-    <t>0x9A</t>
-  </si>
-  <si>
-    <t>Destio</t>
-  </si>
-  <si>
-    <t>Asty</t>
-  </si>
-  <si>
-    <t>Effris</t>
-  </si>
-  <si>
     <t>0x9D</t>
   </si>
   <si>
-    <t>Dancer ?</t>
-  </si>
-  <si>
-    <t>Spellranger ?</t>
-  </si>
-  <si>
     <t>Crimecaster ?</t>
   </si>
   <si>
@@ -1248,9 +1197,6 @@
     <t>Imbertus</t>
   </si>
   <si>
-    <t>Triena</t>
-  </si>
-  <si>
     <t>Reginald</t>
   </si>
   <si>
@@ -1317,34 +1263,19 @@
     <t>Bow Cavalier 6</t>
   </si>
   <si>
-    <t>Peat</t>
-  </si>
-  <si>
-    <t>Wyvern Rider ?</t>
-  </si>
-  <si>
-    <t>Fanilye</t>
-  </si>
-  <si>
-    <t>0x9F</t>
-  </si>
-  <si>
-    <t>Sword Pegasus ?</t>
-  </si>
-  <si>
     <t>Supplier 8</t>
   </si>
   <si>
     <t>REMOVED CHARACTERS</t>
   </si>
   <si>
-    <t>Hime, Suguri, Leon (Ch5)</t>
-  </si>
-  <si>
-    <t>Isabell (Ch4)</t>
-  </si>
-  <si>
-    <t>Alicia (Ch6)</t>
+    <t>Suguri → Ch9</t>
+  </si>
+  <si>
+    <t>Alicia?</t>
+  </si>
+  <si>
+    <t>Alesia?</t>
   </si>
 </sst>
 </file>
@@ -1665,7 +1596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G184"/>
+  <dimension ref="A1:G176"/>
   <sheetFormatPr defaultColWidth="22" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" style="1"/>
@@ -1693,7 +1624,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>436</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -1713,7 +1644,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1733,7 +1664,7 @@
         <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1753,21 +1684,21 @@
         <v>9</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>439</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>9</v>
@@ -1928,16 +1859,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B18" s="1">
         <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>33</v>
@@ -1945,7 +1876,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B19" s="1">
         <v>3</v>
@@ -1954,7 +1885,7 @@
         <v>64</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>9</v>
@@ -1996,7 +1927,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B23" s="1">
         <v>4</v>
@@ -2005,7 +1936,7 @@
         <v>51</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>52</v>
@@ -2013,36 +1944,36 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B24" s="1">
         <v>4</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B25" s="1">
         <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -2076,12 +2007,12 @@
         <v>63</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B30" s="1">
         <v>6</v>
@@ -2090,10 +2021,10 @@
         <v>140</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -2110,12 +2041,12 @@
         <v>67</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B32" s="1">
         <v>6</v>
@@ -2124,7 +2055,7 @@
         <v>141</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>9</v>
@@ -2132,7 +2063,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B33" s="1">
         <v>6</v>
@@ -2141,32 +2072,32 @@
         <v>138</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B34" s="1">
         <v>6</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B35" s="1">
         <v>6</v>
@@ -2175,24 +2106,24 @@
         <v>127</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B37" s="1">
         <v>7</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>9</v>
@@ -2200,84 +2131,84 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>147</v>
+        <v>246</v>
       </c>
       <c r="B38" s="1">
         <v>7</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>148</v>
+        <v>247</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>373</v>
+        <v>248</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>249</v>
+        <v>110</v>
       </c>
       <c r="B39" s="1">
         <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>250</v>
+        <v>152</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>251</v>
+        <v>111</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B40" s="1">
-        <v>7</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="B41" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>154</v>
+        <v>70</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>248</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" s="1">
+        <v>8</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>13</v>
+        <v>249</v>
       </c>
       <c r="B43" s="1">
         <v>8</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>71</v>
+        <v>251</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>9</v>
@@ -2285,186 +2216,163 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="B44" s="1">
         <v>8</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>9</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B45" s="1">
         <v>8</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>165</v>
+        <v>212</v>
       </c>
       <c r="B46" s="1">
         <v>8</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B47" s="1">
-        <v>8</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B48" s="1">
+        <v>9</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="B49" s="1">
         <v>9</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>347</v>
+        <v>411</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B50" s="1">
-        <v>9</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>396</v>
+        <v>77</v>
       </c>
       <c r="B51" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>429</v>
+        <v>79</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>430</v>
+        <v>80</v>
       </c>
       <c r="B52" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>381</v>
+        <v>81</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B53" s="1">
+        <v>10</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>77</v>
+        <v>390</v>
       </c>
       <c r="B54" s="1">
         <v>10</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B55" s="1">
-        <v>10</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>9</v>
+        <v>381</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B56" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>255</v>
+        <v>90</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>9</v>
@@ -2472,112 +2380,135 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>408</v>
+        <v>87</v>
       </c>
       <c r="B57" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>398</v>
+        <v>88</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B58" s="1">
+        <v>11</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="B59" s="1">
         <v>11</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>86</v>
+        <v>168</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>9</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>87</v>
+        <v>228</v>
       </c>
       <c r="B60" s="1">
         <v>11</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>88</v>
+        <v>229</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B61" s="1">
-        <v>11</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>168</v>
+        <v>241</v>
       </c>
       <c r="B62" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>169</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="B63" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>231</v>
+        <v>91</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>151</v>
+        <v>215</v>
       </c>
       <c r="E63" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" s="1">
+        <v>12</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>243</v>
+        <v>95</v>
       </c>
       <c r="B65" s="1">
         <v>12</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>20</v>
@@ -2585,152 +2516,123 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>263</v>
+        <v>160</v>
       </c>
       <c r="B66" s="1">
         <v>12</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>217</v>
+        <v>162</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>92</v>
+        <v>223</v>
       </c>
       <c r="B67" s="1">
         <v>12</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>93</v>
+        <v>196</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>94</v>
+        <v>222</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B68" s="1">
-        <v>12</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E68" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="B69" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>163</v>
+        <v>68</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>164</v>
+        <v>69</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>225</v>
+        <v>156</v>
       </c>
       <c r="B70" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>20</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B71" s="1">
+        <v>13</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="B72" s="1">
         <v>13</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>69</v>
+        <v>265</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B73" s="1">
-        <v>13</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="E73" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="B74" s="1">
-        <v>13</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>20</v>
+        <v>262</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>112</v>
+        <v>365</v>
       </c>
       <c r="B75" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>9</v>
@@ -2738,38 +2640,50 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>114</v>
+        <v>366</v>
       </c>
       <c r="B76" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>268</v>
+        <v>103</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E77" s="1" t="s">
-        <v>265</v>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B78" s="1">
+        <v>15</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>371</v>
+        <v>122</v>
       </c>
       <c r="B79" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>9</v>
@@ -2777,1291 +2691,1181 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>372</v>
+        <v>142</v>
       </c>
       <c r="B80" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B81" s="1">
+        <v>15</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>207</v>
+        <v>360</v>
       </c>
       <c r="B82" s="1">
         <v>15</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>107</v>
+        <v>361</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B83" s="1">
-        <v>15</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>9</v>
+        <v>209</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>142</v>
+        <v>192</v>
       </c>
       <c r="B84" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>9</v>
+        <v>263</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B85" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>185</v>
+        <v>263</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>366</v>
+        <v>264</v>
       </c>
       <c r="B86" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>367</v>
+        <v>188</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>423</v>
+        <v>99</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B88" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B87" s="1">
         <v>16</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E88" s="1" t="s">
+      <c r="C87" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>266</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="B89" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>197</v>
+        <v>129</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>266</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>267</v>
+        <v>131</v>
       </c>
       <c r="B90" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>99</v>
+        <v>402</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="B91" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>269</v>
+        <v>135</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>20</v>
       </c>
     </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B92" s="1">
+        <v>17</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B93" s="1">
         <v>17</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>20</v>
+        <v>396</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>131</v>
+        <v>397</v>
       </c>
       <c r="B94" s="1">
         <v>17</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>132</v>
+        <v>401</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>420</v>
+        <v>126</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B95" s="1">
-        <v>17</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>219</v>
+        <v>176</v>
       </c>
       <c r="B96" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B97" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>414</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>415</v>
+        <v>213</v>
       </c>
       <c r="B98" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>419</v>
+        <v>173</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>126</v>
+        <v>214</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B100" s="1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B99" s="1">
         <v>18</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>180</v>
+      <c r="C99" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="B101" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>118</v>
+        <v>186</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>20</v>
+        <v>267</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="B102" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>211</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="B103" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>213</v>
+        <v>126</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>211</v>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B104" s="1">
+        <v>19</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>186</v>
+        <v>226</v>
       </c>
       <c r="B105" s="1">
         <v>19</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>188</v>
+        <v>403</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>270</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>181</v>
+        <v>294</v>
       </c>
       <c r="B106" s="1">
         <v>19</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>153</v>
+        <v>295</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>400</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B107" s="1">
-        <v>19</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>176</v>
+        <v>319</v>
       </c>
       <c r="B108" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>426</v>
+        <v>317</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B109" s="1">
-        <v>19</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>9</v>
+        <v>209</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>297</v>
+        <v>234</v>
       </c>
       <c r="B110" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>298</v>
+        <v>18</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>418</v>
+        <v>235</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B111" s="1">
+        <v>21</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>322</v>
+        <v>197</v>
       </c>
       <c r="B112" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>323</v>
+        <v>198</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>320</v>
+        <v>225</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="B114" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>20</v>
+        <v>362</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B115" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>190</v>
+        <v>284</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>226</v>
+        <v>280</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>199</v>
+        <v>291</v>
       </c>
       <c r="B116" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>200</v>
+        <v>292</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>227</v>
+        <v>398</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B118" s="1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B117" s="1">
         <v>22</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>368</v>
+      <c r="C117" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>286</v>
+        <v>395</v>
       </c>
       <c r="B119" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>211</v>
+        <v>367</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="B120" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>211</v>
+        <v>363</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>156</v>
+        <v>312</v>
       </c>
       <c r="B121" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>157</v>
+        <v>313</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>424</v>
+        <v>314</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="B123" s="1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B122" s="1">
         <v>23</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>374</v>
+      <c r="C122" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>272</v>
+        <v>338</v>
       </c>
       <c r="B124" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="B125" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>316</v>
+        <v>108</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>317</v>
+        <v>109</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>211</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="B126" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B128" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B127" s="1">
         <v>24</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="E128" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>348</v>
+        <v>277</v>
       </c>
       <c r="B129" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>108</v>
+        <v>278</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>109</v>
+        <v>280</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>349</v>
+        <v>281</v>
       </c>
       <c r="B130" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>351</v>
+        <v>279</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>353</v>
+        <v>282</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="B131" s="1">
-        <v>24</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>20</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B132" s="1">
+        <v>26</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>280</v>
+        <v>377</v>
       </c>
       <c r="B133" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>281</v>
+        <v>378</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>283</v>
+        <v>399</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>284</v>
+        <v>392</v>
       </c>
       <c r="B134" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>282</v>
+        <v>383</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>285</v>
+        <v>384</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="B135" s="1">
-        <v>25</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>385</v>
+        <v>307</v>
       </c>
       <c r="B136" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>382</v>
+        <v>308</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>388</v>
+        <v>309</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>386</v>
+        <v>326</v>
       </c>
       <c r="B137" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>383</v>
+        <v>327</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>389</v>
+        <v>328</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B138" s="1">
+        <v>27</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>304</v>
+        <v>387</v>
       </c>
       <c r="B139" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>305</v>
+        <v>385</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>306</v>
+        <v>386</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="B140" s="1">
-        <v>26</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>410</v>
+        <v>274</v>
       </c>
       <c r="B141" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>400</v>
+        <v>275</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>401</v>
+        <v>276</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>326</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B142" s="1">
+        <v>28</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="B143" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B144" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B145" s="1">
-        <v>27</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>404</v>
+        <v>296</v>
       </c>
       <c r="B146" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>402</v>
+        <v>297</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>403</v>
+        <v>293</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A148" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B148" s="1">
-        <v>28</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B147" s="1">
+        <v>29</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>14</v>
+        <v>272</v>
       </c>
       <c r="B149" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>15</v>
+        <v>273</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>16</v>
+        <v>404</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>335</v>
+        <v>285</v>
       </c>
       <c r="B150" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>336</v>
+        <v>286</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>337</v>
+        <v>407</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="B151" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="B153" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B154" s="1">
+        <v>31</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B154" s="1">
-        <v>29</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="D154" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A155" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="B155" s="1">
-        <v>29</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A157" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B157" s="1">
-        <v>30</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B156" s="1">
+        <v>32</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="B158" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>425</v>
+        <v>317</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>211</v>
+        <v>318</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="B159" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>290</v>
+        <v>335</v>
       </c>
       <c r="B161" s="1">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>291</v>
+        <v>336</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>283</v>
+        <v>337</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="B162" s="1">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B164" s="1">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A166" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B166" s="1">
-        <v>33</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>321</v>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B165" s="1">
+        <v>35</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>405</v>
+        <v>289</v>
       </c>
       <c r="B167" s="1">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>387</v>
+        <v>290</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>390</v>
+        <v>280</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>211</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>338</v>
+        <v>298</v>
       </c>
       <c r="B169" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>339</v>
+        <v>299</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="B170" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>399</v>
+        <v>322</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>362</v>
+        <v>239</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A172" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="B172" s="1">
-        <v>35</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A173" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="B173" s="1">
-        <v>35</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A175" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B175" s="1">
-        <v>36</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A177" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B177" s="1">
-        <v>37</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A178" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B174" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B178" s="1">
-        <v>37</v>
-      </c>
-      <c r="C178" s="1" t="s">
+      <c r="B176" s="1">
+        <v>40</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D178" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B180" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B182" s="1">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A184" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B184" s="1">
-        <v>40</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>211</v>
+      <c r="D176" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
